--- a/docs/demo/davamiyyet.xlsx
+++ b/docs/demo/davamiyyet.xlsx
@@ -442,16 +442,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="2">
-        <v>46301.0</v>
+        <v>46300.0</v>
       </c>
       <c r="D1" s="2">
-        <v>46303.0</v>
+        <v>46302.0</v>
       </c>
       <c r="E1" s="2">
-        <v>46305.0</v>
+        <v>46304.0</v>
       </c>
       <c r="F1" s="2">
-        <v>46308.0</v>
+        <v>46307.0</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
